--- a/outputs/obésité/obésité_annotations_gold_flat.xlsx
+++ b/outputs/obésité/obésité_annotations_gold_flat.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,243 +413,253 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU374"/>
+  <dimension ref="A1:AW374"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>idx</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>NAME</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>TIME</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>TEXT</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>ROLE</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>HATE</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>TARGET</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>VERBAL_ABUSE</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>INTENTION</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>CONTEXT</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>SENTIMENT</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Colère</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Dégoût</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Joie</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Peur</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Surprise</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Tristesse</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Admiration</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Culpabilité</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Embarras</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Fierté</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Jalousie</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Autre</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>n_spans</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>spans_json</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>span1_text</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>span2_text</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>span3_text</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>span4_text</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>span1_cat</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>span2_cat</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>span3_cat</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>span4_cat</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>span1_mode</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>span2_mode</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>span3_mode</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>span4_mode</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>n_disagreements</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>Comportementale</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>Désignée</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>Montrée</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>Suggérée</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>Emo</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Complexe</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>typo</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>elongation</t>
         </is>
       </c>
     </row>
@@ -805,6 +803,12 @@
       <c r="AU2" t="n">
         <v>0</v>
       </c>
+      <c r="AV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -958,6 +962,12 @@
       <c r="AU3" t="n">
         <v>0</v>
       </c>
+      <c r="AV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1145,6 +1155,12 @@
         <v>1</v>
       </c>
       <c r="AU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1298,6 +1314,12 @@
         <v>1</v>
       </c>
       <c r="AU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1433,6 +1455,12 @@
       <c r="AU6" t="n">
         <v>0</v>
       </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1578,6 +1606,12 @@
       <c r="AU7" t="n">
         <v>0</v>
       </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1741,6 +1775,12 @@
         <v>1</v>
       </c>
       <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1876,6 +1916,12 @@
       <c r="AU9" t="n">
         <v>0</v>
       </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -2027,6 +2073,12 @@
         <v>1</v>
       </c>
       <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2180,6 +2232,12 @@
         <v>0</v>
       </c>
       <c r="AU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2323,6 +2381,12 @@
       <c r="AU12" t="n">
         <v>0</v>
       </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2474,6 +2538,12 @@
         <v>1</v>
       </c>
       <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2609,6 +2679,12 @@
       <c r="AU14" t="n">
         <v>0</v>
       </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2766,6 +2842,12 @@
       <c r="AU15" t="n">
         <v>0</v>
       </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2909,6 +2991,12 @@
         <v>1</v>
       </c>
       <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3052,6 +3140,12 @@
       <c r="AU17" t="n">
         <v>0</v>
       </c>
+      <c r="AV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -3205,6 +3299,12 @@
       <c r="AU18" t="n">
         <v>0</v>
       </c>
+      <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3368,6 +3468,12 @@
         <v>1</v>
       </c>
       <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3503,6 +3609,12 @@
       <c r="AU20" t="n">
         <v>0</v>
       </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3644,6 +3756,12 @@
       <c r="AU21" t="n">
         <v>0</v>
       </c>
+      <c r="AV21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3795,6 +3913,12 @@
         <v>1</v>
       </c>
       <c r="AU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3926,6 +4050,12 @@
       <c r="AU23" t="n">
         <v>0</v>
       </c>
+      <c r="AV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -4055,6 +4185,12 @@
       <c r="AU24" t="n">
         <v>0</v>
       </c>
+      <c r="AV24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -4184,6 +4320,12 @@
       <c r="AU25" t="n">
         <v>0</v>
       </c>
+      <c r="AV25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -4325,6 +4467,12 @@
       <c r="AU26" t="n">
         <v>0</v>
       </c>
+      <c r="AV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -4478,6 +4626,12 @@
       <c r="AU27" t="n">
         <v>0</v>
       </c>
+      <c r="AV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4629,6 +4783,12 @@
         <v>1</v>
       </c>
       <c r="AU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4772,6 +4932,12 @@
       <c r="AU29" t="n">
         <v>0</v>
       </c>
+      <c r="AV29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4905,6 +5071,12 @@
       <c r="AU30" t="n">
         <v>0</v>
       </c>
+      <c r="AV30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -5046,6 +5218,12 @@
       <c r="AU31" t="n">
         <v>0</v>
       </c>
+      <c r="AV31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -5193,6 +5371,12 @@
         <v>1</v>
       </c>
       <c r="AU32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5328,6 +5512,12 @@
       <c r="AU33" t="n">
         <v>0</v>
       </c>
+      <c r="AV33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -5461,6 +5651,12 @@
       <c r="AU34" t="n">
         <v>0</v>
       </c>
+      <c r="AV34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -5612,6 +5808,12 @@
         <v>1</v>
       </c>
       <c r="AU35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5747,6 +5949,12 @@
       <c r="AU36" t="n">
         <v>0</v>
       </c>
+      <c r="AV36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5900,6 +6108,12 @@
       <c r="AU37" t="n">
         <v>0</v>
       </c>
+      <c r="AV37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -6053,6 +6267,12 @@
       <c r="AU38" t="n">
         <v>0</v>
       </c>
+      <c r="AV38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -6230,6 +6450,12 @@
       <c r="AU39" t="n">
         <v>0</v>
       </c>
+      <c r="AV39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -6374,6 +6600,12 @@
       </c>
       <c r="AU40" t="n">
         <v>0</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -6506,6 +6738,12 @@
         <v>0</v>
       </c>
       <c r="AU41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6649,6 +6887,12 @@
       <c r="AU42" t="n">
         <v>0</v>
       </c>
+      <c r="AV42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -6800,6 +7044,12 @@
         <v>1</v>
       </c>
       <c r="AU43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW43" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6943,6 +7193,12 @@
       <c r="AU44" t="n">
         <v>0</v>
       </c>
+      <c r="AV44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -7120,6 +7376,12 @@
       <c r="AU45" t="n">
         <v>0</v>
       </c>
+      <c r="AV45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW45" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -7283,6 +7545,12 @@
         <v>1</v>
       </c>
       <c r="AU46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW46" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7426,6 +7694,12 @@
       <c r="AU47" t="n">
         <v>0</v>
       </c>
+      <c r="AV47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW47" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -7559,6 +7833,12 @@
       <c r="AU48" t="n">
         <v>0</v>
       </c>
+      <c r="AV48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW48" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -7710,6 +7990,12 @@
         <v>1</v>
       </c>
       <c r="AU49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW49" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7865,6 +8151,12 @@
       <c r="AU50" t="n">
         <v>0</v>
       </c>
+      <c r="AV50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW50" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -8024,6 +8316,12 @@
         <v>1</v>
       </c>
       <c r="AU51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW51" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8159,6 +8457,12 @@
       <c r="AU52" t="n">
         <v>0</v>
       </c>
+      <c r="AV52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW52" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -8300,6 +8604,12 @@
       <c r="AU53" t="n">
         <v>0</v>
       </c>
+      <c r="AV53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW53" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -8433,6 +8743,12 @@
       <c r="AU54" t="n">
         <v>0</v>
       </c>
+      <c r="AV54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW54" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -8586,6 +8902,12 @@
       <c r="AU55" t="n">
         <v>0</v>
       </c>
+      <c r="AV55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW55" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -8751,6 +9073,12 @@
       <c r="AU56" t="n">
         <v>0</v>
       </c>
+      <c r="AV56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW56" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -8902,6 +9230,12 @@
         <v>1</v>
       </c>
       <c r="AU57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW57" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9037,6 +9371,12 @@
       <c r="AU58" t="n">
         <v>0</v>
       </c>
+      <c r="AV58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW58" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -9182,6 +9522,12 @@
       <c r="AU59" t="n">
         <v>0</v>
       </c>
+      <c r="AV59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW59" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -9333,6 +9679,12 @@
         <v>1</v>
       </c>
       <c r="AU60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW60" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9464,6 +9816,12 @@
       <c r="AU61" t="n">
         <v>0</v>
       </c>
+      <c r="AV61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW61" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -9615,6 +9973,12 @@
         <v>1</v>
       </c>
       <c r="AU62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW62" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9750,6 +10114,12 @@
       <c r="AU63" t="n">
         <v>0</v>
       </c>
+      <c r="AV63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW63" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -9899,6 +10269,12 @@
       <c r="AU64" t="n">
         <v>0</v>
       </c>
+      <c r="AV64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW64" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -10052,6 +10428,12 @@
       <c r="AU65" t="n">
         <v>0</v>
       </c>
+      <c r="AV65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW65" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -10205,6 +10587,12 @@
       <c r="AU66" t="n">
         <v>0</v>
       </c>
+      <c r="AV66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW66" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -10358,6 +10746,12 @@
       <c r="AU67" t="n">
         <v>0</v>
       </c>
+      <c r="AV67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW67" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -10505,6 +10899,12 @@
         <v>1</v>
       </c>
       <c r="AU68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW68" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10640,6 +11040,12 @@
       <c r="AU69" t="n">
         <v>0</v>
       </c>
+      <c r="AV69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW69" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -10805,6 +11211,12 @@
       <c r="AU70" t="n">
         <v>0</v>
       </c>
+      <c r="AV70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW70" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -10956,6 +11368,12 @@
         <v>1</v>
       </c>
       <c r="AU71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW71" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11091,6 +11509,12 @@
       <c r="AU72" t="n">
         <v>0</v>
       </c>
+      <c r="AV72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW72" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -11242,6 +11666,12 @@
         <v>0</v>
       </c>
       <c r="AU73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW73" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11385,6 +11815,12 @@
       <c r="AU74" t="n">
         <v>0</v>
       </c>
+      <c r="AV74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW74" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -11538,6 +11974,12 @@
       <c r="AU75" t="n">
         <v>0</v>
       </c>
+      <c r="AV75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW75" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -11691,6 +12133,12 @@
       <c r="AU76" t="n">
         <v>0</v>
       </c>
+      <c r="AV76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW76" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -11844,6 +12292,12 @@
       <c r="AU77" t="n">
         <v>0</v>
       </c>
+      <c r="AV77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW77" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -11997,6 +12451,12 @@
       <c r="AU78" t="n">
         <v>0</v>
       </c>
+      <c r="AV78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW78" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -12162,6 +12622,12 @@
       <c r="AU79" t="n">
         <v>0</v>
       </c>
+      <c r="AV79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW79" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -12313,6 +12779,12 @@
         <v>1</v>
       </c>
       <c r="AU80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW80" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12456,6 +12928,12 @@
       <c r="AU81" t="n">
         <v>0</v>
       </c>
+      <c r="AV81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW81" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -12597,6 +13075,12 @@
       <c r="AU82" t="n">
         <v>0</v>
       </c>
+      <c r="AV82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW82" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -12762,6 +13246,12 @@
       <c r="AU83" t="n">
         <v>0</v>
       </c>
+      <c r="AV83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW83" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -12901,6 +13391,12 @@
         <v>1</v>
       </c>
       <c r="AU84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW84" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13056,6 +13552,12 @@
       <c r="AU85" t="n">
         <v>0</v>
       </c>
+      <c r="AV85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW85" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -13207,6 +13709,12 @@
         <v>1</v>
       </c>
       <c r="AU86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW86" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13350,6 +13858,12 @@
       <c r="AU87" t="n">
         <v>0</v>
       </c>
+      <c r="AV87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW87" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -13491,6 +14005,12 @@
       <c r="AU88" t="n">
         <v>0</v>
       </c>
+      <c r="AV88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW88" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -13644,6 +14164,12 @@
       <c r="AU89" t="n">
         <v>0</v>
       </c>
+      <c r="AV89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW89" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -13821,6 +14347,12 @@
       <c r="AU90" t="n">
         <v>0</v>
       </c>
+      <c r="AV90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW90" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -13972,6 +14504,12 @@
         <v>1</v>
       </c>
       <c r="AU91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW91" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14115,6 +14653,12 @@
       <c r="AU92" t="n">
         <v>0</v>
       </c>
+      <c r="AV92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW92" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -14266,6 +14810,12 @@
         <v>0</v>
       </c>
       <c r="AU93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW93" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14409,6 +14959,12 @@
       <c r="AU94" t="n">
         <v>0</v>
       </c>
+      <c r="AV94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW94" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -14550,6 +15106,12 @@
       <c r="AU95" t="n">
         <v>0</v>
       </c>
+      <c r="AV95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW95" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -14701,6 +15263,12 @@
         <v>1</v>
       </c>
       <c r="AU96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW96" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14836,6 +15404,12 @@
       <c r="AU97" t="n">
         <v>0</v>
       </c>
+      <c r="AV97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW97" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -14977,6 +15551,12 @@
       <c r="AU98" t="n">
         <v>0</v>
       </c>
+      <c r="AV98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW98" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -15118,6 +15698,12 @@
       <c r="AU99" t="n">
         <v>0</v>
       </c>
+      <c r="AV99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW99" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -15251,6 +15837,12 @@
       <c r="AU100" t="n">
         <v>0</v>
       </c>
+      <c r="AV100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW100" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -15384,6 +15976,12 @@
       <c r="AU101" t="n">
         <v>0</v>
       </c>
+      <c r="AV101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW101" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -15523,6 +16121,12 @@
         <v>1</v>
       </c>
       <c r="AU102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW102" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15662,6 +16266,12 @@
       <c r="AU103" t="n">
         <v>0</v>
       </c>
+      <c r="AV103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW103" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -15819,6 +16429,12 @@
       <c r="AU104" t="n">
         <v>0</v>
       </c>
+      <c r="AV104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW104" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -15996,6 +16612,12 @@
       <c r="AU105" t="n">
         <v>0</v>
       </c>
+      <c r="AV105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW105" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -16161,6 +16783,12 @@
       <c r="AU106" t="n">
         <v>0</v>
       </c>
+      <c r="AV106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW106" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -16314,6 +16942,12 @@
       <c r="AU107" t="n">
         <v>0</v>
       </c>
+      <c r="AV107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW107" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -16457,6 +17091,12 @@
         <v>1</v>
       </c>
       <c r="AU108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW108" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16600,6 +17240,12 @@
       <c r="AU109" t="n">
         <v>0</v>
       </c>
+      <c r="AV109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW109" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -16765,6 +17411,12 @@
       <c r="AU110" t="n">
         <v>0</v>
       </c>
+      <c r="AV110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW110" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -16918,6 +17570,12 @@
       <c r="AU111" t="n">
         <v>0</v>
       </c>
+      <c r="AV111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW111" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -17081,6 +17739,12 @@
         <v>1</v>
       </c>
       <c r="AU112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW112" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17224,6 +17888,12 @@
       <c r="AU113" t="n">
         <v>0</v>
       </c>
+      <c r="AV113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW113" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -17387,6 +18057,12 @@
         <v>1</v>
       </c>
       <c r="AU114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW114" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17528,6 +18204,12 @@
         <v>0</v>
       </c>
       <c r="AU115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW115" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17671,6 +18353,12 @@
       <c r="AU116" t="n">
         <v>0</v>
       </c>
+      <c r="AV116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW116" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -17814,6 +18502,12 @@
         <v>1</v>
       </c>
       <c r="AU117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW117" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17957,6 +18651,12 @@
       <c r="AU118" t="n">
         <v>0</v>
       </c>
+      <c r="AV118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -18108,6 +18808,12 @@
         <v>1</v>
       </c>
       <c r="AU119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW119" t="n">
         <v>0</v>
       </c>
     </row>
@@ -18251,6 +18957,12 @@
       <c r="AU120" t="n">
         <v>0</v>
       </c>
+      <c r="AV120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -18404,6 +19116,12 @@
       <c r="AU121" t="n">
         <v>0</v>
       </c>
+      <c r="AV121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -18559,6 +19277,12 @@
         <v>1</v>
       </c>
       <c r="AU122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW122" t="n">
         <v>0</v>
       </c>
     </row>
@@ -18702,6 +19426,12 @@
       <c r="AU123" t="n">
         <v>0</v>
       </c>
+      <c r="AV123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -18855,6 +19585,12 @@
       <c r="AU124" t="n">
         <v>0</v>
       </c>
+      <c r="AV124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -19018,6 +19754,12 @@
         <v>1</v>
       </c>
       <c r="AU125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW125" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19161,6 +19903,12 @@
       <c r="AU126" t="n">
         <v>0</v>
       </c>
+      <c r="AV126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -19294,6 +20042,12 @@
       <c r="AU127" t="n">
         <v>0</v>
       </c>
+      <c r="AV127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -19427,6 +20181,12 @@
       <c r="AU128" t="n">
         <v>0</v>
       </c>
+      <c r="AV128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -19568,6 +20328,12 @@
       <c r="AU129" t="n">
         <v>0</v>
       </c>
+      <c r="AV129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -19701,6 +20467,12 @@
       <c r="AU130" t="n">
         <v>0</v>
       </c>
+      <c r="AV130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -19842,6 +20614,12 @@
       <c r="AU131" t="n">
         <v>0</v>
       </c>
+      <c r="AV131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -19979,6 +20757,12 @@
       <c r="AU132" t="n">
         <v>0</v>
       </c>
+      <c r="AV132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -20120,6 +20904,12 @@
       <c r="AU133" t="n">
         <v>0</v>
       </c>
+      <c r="AV133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -20271,6 +21061,12 @@
         <v>1</v>
       </c>
       <c r="AU134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW134" t="n">
         <v>0</v>
       </c>
     </row>
@@ -20406,6 +21202,12 @@
       <c r="AU135" t="n">
         <v>0</v>
       </c>
+      <c r="AV135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -20559,6 +21361,12 @@
       <c r="AU136" t="n">
         <v>0</v>
       </c>
+      <c r="AV136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -20712,6 +21520,12 @@
       <c r="AU137" t="n">
         <v>0</v>
       </c>
+      <c r="AV137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -20855,6 +21669,12 @@
         <v>1</v>
       </c>
       <c r="AU138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW138" t="n">
         <v>0</v>
       </c>
     </row>
@@ -20994,6 +21814,12 @@
       <c r="AU139" t="n">
         <v>0</v>
       </c>
+      <c r="AV139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -21139,6 +21965,12 @@
       <c r="AU140" t="n">
         <v>0</v>
       </c>
+      <c r="AV140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -21290,6 +22122,12 @@
         <v>1</v>
       </c>
       <c r="AU141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW141" t="n">
         <v>0</v>
       </c>
     </row>
@@ -21433,6 +22271,12 @@
       <c r="AU142" t="n">
         <v>0</v>
       </c>
+      <c r="AV142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -21586,6 +22430,12 @@
       <c r="AU143" t="n">
         <v>0</v>
       </c>
+      <c r="AV143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -21749,6 +22599,12 @@
         <v>1</v>
       </c>
       <c r="AU144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW144" t="n">
         <v>0</v>
       </c>
     </row>
@@ -21880,6 +22736,12 @@
       <c r="AU145" t="n">
         <v>0</v>
       </c>
+      <c r="AV145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW145" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -22021,6 +22883,12 @@
       <c r="AU146" t="n">
         <v>0</v>
       </c>
+      <c r="AV146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW146" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -22174,6 +23042,12 @@
       <c r="AU147" t="n">
         <v>0</v>
       </c>
+      <c r="AV147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW147" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -22319,6 +23193,12 @@
       <c r="AU148" t="n">
         <v>0</v>
       </c>
+      <c r="AV148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW148" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -22472,6 +23352,12 @@
       <c r="AU149" t="n">
         <v>0</v>
       </c>
+      <c r="AV149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW149" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -22613,6 +23499,12 @@
       <c r="AU150" t="n">
         <v>0</v>
       </c>
+      <c r="AV150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW150" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -22778,6 +23670,12 @@
       <c r="AU151" t="n">
         <v>0</v>
       </c>
+      <c r="AV151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW151" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -22919,6 +23817,12 @@
       <c r="AU152" t="n">
         <v>0</v>
       </c>
+      <c r="AV152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW152" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -23070,6 +23974,12 @@
         <v>1</v>
       </c>
       <c r="AU153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW153" t="n">
         <v>0</v>
       </c>
     </row>
@@ -23225,6 +24135,12 @@
       <c r="AU154" t="n">
         <v>0</v>
       </c>
+      <c r="AV154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW154" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -23386,6 +24302,12 @@
       <c r="AU155" t="n">
         <v>0</v>
       </c>
+      <c r="AV155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW155" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -23539,6 +24461,12 @@
       <c r="AU156" t="n">
         <v>0</v>
       </c>
+      <c r="AV156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW156" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -23692,6 +24620,12 @@
       <c r="AU157" t="n">
         <v>0</v>
       </c>
+      <c r="AV157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW157" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -23835,6 +24769,12 @@
         <v>1</v>
       </c>
       <c r="AU158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW158" t="n">
         <v>0</v>
       </c>
     </row>
@@ -23970,6 +24910,12 @@
       <c r="AU159" t="n">
         <v>0</v>
       </c>
+      <c r="AV159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW159" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -24145,6 +25091,12 @@
         <v>1</v>
       </c>
       <c r="AU160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW160" t="n">
         <v>0</v>
       </c>
     </row>
@@ -24280,6 +25232,12 @@
       <c r="AU161" t="n">
         <v>0</v>
       </c>
+      <c r="AV161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW161" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -24413,6 +25371,12 @@
       <c r="AU162" t="n">
         <v>0</v>
       </c>
+      <c r="AV162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW162" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -24554,6 +25518,12 @@
       <c r="AU163" t="n">
         <v>0</v>
       </c>
+      <c r="AV163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW163" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -24687,6 +25657,12 @@
       <c r="AU164" t="n">
         <v>0</v>
       </c>
+      <c r="AV164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW164" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -24840,6 +25816,12 @@
       <c r="AU165" t="n">
         <v>0</v>
       </c>
+      <c r="AV165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW165" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -24993,6 +25975,12 @@
       <c r="AU166" t="n">
         <v>0</v>
       </c>
+      <c r="AV166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW166" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -25144,6 +26132,12 @@
         <v>1</v>
       </c>
       <c r="AU167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW167" t="n">
         <v>0</v>
       </c>
     </row>
@@ -25279,6 +26273,12 @@
       <c r="AU168" t="n">
         <v>0</v>
       </c>
+      <c r="AV168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW168" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -25420,6 +26420,12 @@
       <c r="AU169" t="n">
         <v>0</v>
       </c>
+      <c r="AV169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW169" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -25573,6 +26579,12 @@
       <c r="AU170" t="n">
         <v>0</v>
       </c>
+      <c r="AV170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW170" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -25732,6 +26744,12 @@
         <v>1</v>
       </c>
       <c r="AU171" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV171" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW171" t="n">
         <v>0</v>
       </c>
     </row>
@@ -25879,6 +26897,12 @@
       <c r="AU172" t="n">
         <v>0</v>
       </c>
+      <c r="AV172" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW172" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -26032,6 +27056,12 @@
       <c r="AU173" t="n">
         <v>0</v>
       </c>
+      <c r="AV173" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW173" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -26185,6 +27215,12 @@
       <c r="AU174" t="n">
         <v>0</v>
       </c>
+      <c r="AV174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW174" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -26332,6 +27368,12 @@
         <v>1</v>
       </c>
       <c r="AU175" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV175" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW175" t="n">
         <v>0</v>
       </c>
     </row>
@@ -26467,6 +27509,12 @@
       <c r="AU176" t="n">
         <v>0</v>
       </c>
+      <c r="AV176" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW176" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -26600,6 +27648,12 @@
       <c r="AU177" t="n">
         <v>0</v>
       </c>
+      <c r="AV177" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW177" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -26733,6 +27787,12 @@
       <c r="AU178" t="n">
         <v>0</v>
       </c>
+      <c r="AV178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW178" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -26894,6 +27954,12 @@
       <c r="AU179" t="n">
         <v>0</v>
       </c>
+      <c r="AV179" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW179" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -27071,6 +28137,12 @@
       <c r="AU180" t="n">
         <v>0</v>
       </c>
+      <c r="AV180" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW180" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -27220,6 +28292,12 @@
       <c r="AU181" t="n">
         <v>0</v>
       </c>
+      <c r="AV181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW181" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -27359,6 +28437,12 @@
         <v>1</v>
       </c>
       <c r="AU182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW182" t="n">
         <v>0</v>
       </c>
     </row>
@@ -27498,6 +28582,12 @@
       <c r="AU183" t="n">
         <v>0</v>
       </c>
+      <c r="AV183" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW183" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -27653,6 +28743,12 @@
         <v>1</v>
       </c>
       <c r="AU184" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV184" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW184" t="n">
         <v>0</v>
       </c>
     </row>
@@ -27784,6 +28880,12 @@
       <c r="AU185" t="n">
         <v>0</v>
       </c>
+      <c r="AV185" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW185" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -27937,6 +29039,12 @@
       <c r="AU186" t="n">
         <v>0</v>
       </c>
+      <c r="AV186" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW186" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -28126,6 +29234,12 @@
       <c r="AU187" t="n">
         <v>0</v>
       </c>
+      <c r="AV187" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW187" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -28271,6 +29385,12 @@
       <c r="AU188" t="n">
         <v>0</v>
       </c>
+      <c r="AV188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW188" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -28436,6 +29556,12 @@
       <c r="AU189" t="n">
         <v>0</v>
       </c>
+      <c r="AV189" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW189" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -28581,6 +29707,12 @@
       <c r="AU190" t="n">
         <v>0</v>
       </c>
+      <c r="AV190" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW190" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -28746,6 +29878,12 @@
       <c r="AU191" t="n">
         <v>0</v>
       </c>
+      <c r="AV191" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW191" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -28921,6 +30059,12 @@
         <v>1</v>
       </c>
       <c r="AU192" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV192" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW192" t="n">
         <v>0</v>
       </c>
     </row>
@@ -29062,6 +30206,12 @@
         <v>0</v>
       </c>
       <c r="AU193" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV193" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW193" t="n">
         <v>0</v>
       </c>
     </row>
@@ -29205,6 +30355,12 @@
       <c r="AU194" t="n">
         <v>0</v>
       </c>
+      <c r="AV194" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW194" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -29346,6 +30502,12 @@
       <c r="AU195" t="n">
         <v>0</v>
       </c>
+      <c r="AV195" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW195" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -29499,6 +30661,12 @@
       <c r="AU196" t="n">
         <v>0</v>
       </c>
+      <c r="AV196" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW196" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -29640,6 +30808,12 @@
       <c r="AU197" t="n">
         <v>0</v>
       </c>
+      <c r="AV197" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW197" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -29791,6 +30965,12 @@
         <v>1</v>
       </c>
       <c r="AU198" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV198" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW198" t="n">
         <v>0</v>
       </c>
     </row>
@@ -29926,6 +31106,12 @@
       <c r="AU199" t="n">
         <v>0</v>
       </c>
+      <c r="AV199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW199" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -30055,6 +31241,12 @@
       <c r="AU200" t="n">
         <v>0</v>
       </c>
+      <c r="AV200" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW200" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -30196,6 +31388,12 @@
       <c r="AU201" t="n">
         <v>0</v>
       </c>
+      <c r="AV201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW201" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -30329,6 +31527,12 @@
       <c r="AU202" t="n">
         <v>0</v>
       </c>
+      <c r="AV202" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW202" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -30470,6 +31674,12 @@
       <c r="AU203" t="n">
         <v>0</v>
       </c>
+      <c r="AV203" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW203" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -30629,6 +31839,12 @@
         <v>1</v>
       </c>
       <c r="AU204" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV204" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW204" t="n">
         <v>0</v>
       </c>
     </row>
@@ -30772,6 +31988,12 @@
       <c r="AU205" t="n">
         <v>0</v>
       </c>
+      <c r="AV205" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW205" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -30905,6 +32127,12 @@
       <c r="AU206" t="n">
         <v>0</v>
       </c>
+      <c r="AV206" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW206" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -31080,6 +32308,12 @@
         <v>1</v>
       </c>
       <c r="AU207" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV207" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW207" t="n">
         <v>0</v>
       </c>
     </row>
@@ -31223,6 +32457,12 @@
       <c r="AU208" t="n">
         <v>0</v>
       </c>
+      <c r="AV208" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW208" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -31360,6 +32600,12 @@
       <c r="AU209" t="n">
         <v>0</v>
       </c>
+      <c r="AV209" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW209" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -31501,6 +32747,12 @@
       <c r="AU210" t="n">
         <v>0</v>
       </c>
+      <c r="AV210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW210" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -31664,6 +32916,12 @@
         <v>0</v>
       </c>
       <c r="AU211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW211" t="n">
         <v>0</v>
       </c>
     </row>
@@ -31807,6 +33065,12 @@
       <c r="AU212" t="n">
         <v>0</v>
       </c>
+      <c r="AV212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW212" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -31948,6 +33212,12 @@
       <c r="AU213" t="n">
         <v>0</v>
       </c>
+      <c r="AV213" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW213" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -32087,6 +33357,12 @@
         <v>0</v>
       </c>
       <c r="AU214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW214" t="n">
         <v>0</v>
       </c>
     </row>
@@ -32218,6 +33494,12 @@
       <c r="AU215" t="n">
         <v>0</v>
       </c>
+      <c r="AV215" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW215" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -32371,6 +33653,12 @@
       <c r="AU216" t="n">
         <v>0</v>
       </c>
+      <c r="AV216" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW216" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -32535,6 +33823,12 @@
       </c>
       <c r="AU217" t="n">
         <v>1</v>
+      </c>
+      <c r="AV217" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW217" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="218">
@@ -32669,6 +33963,12 @@
       <c r="AU218" t="n">
         <v>0</v>
       </c>
+      <c r="AV218" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW218" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -32812,6 +34112,12 @@
         <v>1</v>
       </c>
       <c r="AU219" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV219" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW219" t="n">
         <v>0</v>
       </c>
     </row>
@@ -32955,6 +34261,12 @@
       <c r="AU220" t="n">
         <v>0</v>
       </c>
+      <c r="AV220" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW220" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -33120,6 +34432,12 @@
       <c r="AU221" t="n">
         <v>0</v>
       </c>
+      <c r="AV221" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW221" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -33295,6 +34613,12 @@
         <v>1</v>
       </c>
       <c r="AU222" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV222" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW222" t="n">
         <v>0</v>
       </c>
     </row>
@@ -33430,6 +34754,12 @@
       <c r="AU223" t="n">
         <v>0</v>
       </c>
+      <c r="AV223" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW223" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -33599,6 +34929,12 @@
       <c r="AU224" t="n">
         <v>0</v>
       </c>
+      <c r="AV224" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW224" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -33752,6 +35088,12 @@
       <c r="AU225" t="n">
         <v>0</v>
       </c>
+      <c r="AV225" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW225" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -33905,6 +35247,12 @@
       <c r="AU226" t="n">
         <v>0</v>
       </c>
+      <c r="AV226" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW226" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -34056,6 +35404,12 @@
         <v>1</v>
       </c>
       <c r="AU227" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV227" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW227" t="n">
         <v>0</v>
       </c>
     </row>
@@ -34199,6 +35553,12 @@
       <c r="AU228" t="n">
         <v>0</v>
       </c>
+      <c r="AV228" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW228" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -34344,6 +35704,12 @@
       <c r="AU229" t="n">
         <v>0</v>
       </c>
+      <c r="AV229" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW229" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -34497,6 +35863,12 @@
       <c r="AU230" t="n">
         <v>0</v>
       </c>
+      <c r="AV230" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW230" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -34640,6 +36012,12 @@
         <v>1</v>
       </c>
       <c r="AU231" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV231" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW231" t="n">
         <v>0</v>
       </c>
     </row>
@@ -34783,6 +36161,12 @@
       <c r="AU232" t="n">
         <v>0</v>
       </c>
+      <c r="AV232" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW232" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -34920,6 +36304,12 @@
       <c r="AU233" t="n">
         <v>0</v>
       </c>
+      <c r="AV233" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW233" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -35049,6 +36439,12 @@
       <c r="AU234" t="n">
         <v>0</v>
       </c>
+      <c r="AV234" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW234" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -35186,6 +36582,12 @@
       <c r="AU235" t="n">
         <v>0</v>
       </c>
+      <c r="AV235" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW235" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -35337,6 +36739,12 @@
         <v>1</v>
       </c>
       <c r="AU236" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV236" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW236" t="n">
         <v>0</v>
       </c>
     </row>
@@ -35480,6 +36888,12 @@
       <c r="AU237" t="n">
         <v>0</v>
       </c>
+      <c r="AV237" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW237" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -35627,6 +37041,12 @@
         <v>1</v>
       </c>
       <c r="AU238" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV238" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW238" t="n">
         <v>0</v>
       </c>
     </row>
@@ -35770,6 +37190,12 @@
       <c r="AU239" t="n">
         <v>0</v>
       </c>
+      <c r="AV239" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW239" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -35923,6 +37349,12 @@
       <c r="AU240" t="n">
         <v>0</v>
       </c>
+      <c r="AV240" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW240" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -36084,6 +37516,12 @@
       <c r="AU241" t="n">
         <v>0</v>
       </c>
+      <c r="AV241" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW241" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -36247,6 +37685,12 @@
         <v>1</v>
       </c>
       <c r="AU242" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV242" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW242" t="n">
         <v>0</v>
       </c>
     </row>
@@ -36390,6 +37834,12 @@
       <c r="AU243" t="n">
         <v>0</v>
       </c>
+      <c r="AV243" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW243" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -36543,6 +37993,12 @@
       <c r="AU244" t="n">
         <v>0</v>
       </c>
+      <c r="AV244" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW244" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -36684,6 +38140,12 @@
       <c r="AU245" t="n">
         <v>1</v>
       </c>
+      <c r="AV245" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW245" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -36837,6 +38299,12 @@
       <c r="AU246" t="n">
         <v>0</v>
       </c>
+      <c r="AV246" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW246" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -36988,6 +38456,12 @@
         <v>1</v>
       </c>
       <c r="AU247" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV247" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW247" t="n">
         <v>0</v>
       </c>
     </row>
@@ -37123,6 +38597,12 @@
       <c r="AU248" t="n">
         <v>0</v>
       </c>
+      <c r="AV248" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW248" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -37270,6 +38750,12 @@
         <v>1</v>
       </c>
       <c r="AU249" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV249" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW249" t="n">
         <v>0</v>
       </c>
     </row>
@@ -37413,6 +38899,12 @@
       <c r="AU250" t="n">
         <v>0</v>
       </c>
+      <c r="AV250" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW250" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -37546,6 +39038,12 @@
       <c r="AU251" t="n">
         <v>0</v>
       </c>
+      <c r="AV251" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW251" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -37691,6 +39189,12 @@
       <c r="AU252" t="n">
         <v>0</v>
       </c>
+      <c r="AV252" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW252" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -37860,6 +39364,12 @@
       <c r="AU253" t="n">
         <v>0</v>
       </c>
+      <c r="AV253" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW253" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -38013,6 +39523,12 @@
       <c r="AU254" t="n">
         <v>0</v>
       </c>
+      <c r="AV254" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW254" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -38178,6 +39694,12 @@
       <c r="AU255" t="n">
         <v>0</v>
       </c>
+      <c r="AV255" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW255" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -38331,6 +39853,12 @@
       <c r="AU256" t="n">
         <v>0</v>
       </c>
+      <c r="AV256" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW256" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -38474,6 +40002,12 @@
         <v>1</v>
       </c>
       <c r="AU257" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV257" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW257" t="n">
         <v>0</v>
       </c>
     </row>
@@ -38609,6 +40143,12 @@
       <c r="AU258" t="n">
         <v>0</v>
       </c>
+      <c r="AV258" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW258" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -38742,6 +40282,12 @@
       <c r="AU259" t="n">
         <v>0</v>
       </c>
+      <c r="AV259" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW259" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -38875,6 +40421,12 @@
       <c r="AU260" t="n">
         <v>0</v>
       </c>
+      <c r="AV260" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW260" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -39012,6 +40564,12 @@
       <c r="AU261" t="n">
         <v>0</v>
       </c>
+      <c r="AV261" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW261" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -39149,6 +40707,12 @@
       <c r="AU262" t="n">
         <v>0</v>
       </c>
+      <c r="AV262" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW262" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -39306,6 +40870,12 @@
       <c r="AU263" t="n">
         <v>0</v>
       </c>
+      <c r="AV263" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW263" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -39459,6 +41029,12 @@
       <c r="AU264" t="n">
         <v>0</v>
       </c>
+      <c r="AV264" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW264" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -39624,6 +41200,12 @@
       <c r="AU265" t="n">
         <v>0</v>
       </c>
+      <c r="AV265" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW265" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -39777,6 +41359,12 @@
       <c r="AU266" t="n">
         <v>0</v>
       </c>
+      <c r="AV266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW266" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -39940,6 +41528,12 @@
         <v>1</v>
       </c>
       <c r="AU267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW267" t="n">
         <v>0</v>
       </c>
     </row>
@@ -40071,6 +41665,12 @@
       <c r="AU268" t="n">
         <v>0</v>
       </c>
+      <c r="AV268" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW268" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -40222,6 +41822,12 @@
         <v>1</v>
       </c>
       <c r="AU269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW269" t="n">
         <v>0</v>
       </c>
     </row>
@@ -40365,6 +41971,12 @@
       <c r="AU270" t="n">
         <v>0</v>
       </c>
+      <c r="AV270" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW270" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -40530,6 +42142,12 @@
       <c r="AU271" t="n">
         <v>0</v>
       </c>
+      <c r="AV271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW271" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -40673,6 +42291,12 @@
         <v>1</v>
       </c>
       <c r="AU272" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV272" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW272" t="n">
         <v>0</v>
       </c>
     </row>
@@ -40804,6 +42428,12 @@
       <c r="AU273" t="n">
         <v>0</v>
       </c>
+      <c r="AV273" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW273" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -40955,6 +42585,12 @@
         <v>1</v>
       </c>
       <c r="AU274" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV274" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW274" t="n">
         <v>0</v>
       </c>
     </row>
@@ -41090,6 +42726,12 @@
       <c r="AU275" t="n">
         <v>0</v>
       </c>
+      <c r="AV275" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW275" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -41223,6 +42865,12 @@
       <c r="AU276" t="n">
         <v>0</v>
       </c>
+      <c r="AV276" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW276" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -41368,6 +43016,12 @@
       <c r="AU277" t="n">
         <v>0</v>
       </c>
+      <c r="AV277" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW277" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -41519,6 +43173,12 @@
         <v>1</v>
       </c>
       <c r="AU278" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV278" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW278" t="n">
         <v>0</v>
       </c>
     </row>
@@ -41662,6 +43322,12 @@
       <c r="AU279" t="n">
         <v>0</v>
       </c>
+      <c r="AV279" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW279" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -41791,6 +43457,12 @@
       <c r="AU280" t="n">
         <v>0</v>
       </c>
+      <c r="AV280" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW280" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -41934,6 +43606,12 @@
         <v>1</v>
       </c>
       <c r="AU281" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV281" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW281" t="n">
         <v>0</v>
       </c>
     </row>
@@ -42065,6 +43743,12 @@
       <c r="AU282" t="n">
         <v>0</v>
       </c>
+      <c r="AV282" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW282" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -42194,6 +43878,12 @@
       <c r="AU283" t="n">
         <v>0</v>
       </c>
+      <c r="AV283" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW283" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -42359,6 +44049,12 @@
       <c r="AU284" t="n">
         <v>0</v>
       </c>
+      <c r="AV284" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW284" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -42498,6 +44194,12 @@
         <v>1</v>
       </c>
       <c r="AU285" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV285" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW285" t="n">
         <v>0</v>
       </c>
     </row>
@@ -42633,6 +44335,12 @@
       <c r="AU286" t="n">
         <v>0</v>
       </c>
+      <c r="AV286" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW286" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -42786,6 +44494,12 @@
       <c r="AU287" t="n">
         <v>0</v>
       </c>
+      <c r="AV287" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW287" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -42939,6 +44653,12 @@
       <c r="AU288" t="n">
         <v>0</v>
       </c>
+      <c r="AV288" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW288" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -43092,6 +44812,12 @@
       <c r="AU289" t="n">
         <v>0</v>
       </c>
+      <c r="AV289" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW289" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -43253,6 +44979,12 @@
       <c r="AU290" t="n">
         <v>0</v>
       </c>
+      <c r="AV290" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW290" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -43404,6 +45136,12 @@
         <v>1</v>
       </c>
       <c r="AU291" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV291" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW291" t="n">
         <v>0</v>
       </c>
     </row>
@@ -43539,6 +45277,12 @@
       <c r="AU292" t="n">
         <v>0</v>
       </c>
+      <c r="AV292" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW292" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -43680,6 +45424,12 @@
       <c r="AU293" t="n">
         <v>0</v>
       </c>
+      <c r="AV293" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW293" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -43843,6 +45593,12 @@
         <v>1</v>
       </c>
       <c r="AU294" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV294" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW294" t="n">
         <v>0</v>
       </c>
     </row>
@@ -43986,6 +45742,12 @@
       <c r="AU295" t="n">
         <v>0</v>
       </c>
+      <c r="AV295" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW295" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -44129,6 +45891,12 @@
         <v>1</v>
       </c>
       <c r="AU296" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV296" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW296" t="n">
         <v>0</v>
       </c>
     </row>
@@ -44268,6 +46036,12 @@
       <c r="AU297" t="n">
         <v>0</v>
       </c>
+      <c r="AV297" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW297" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -44419,6 +46193,12 @@
         <v>1</v>
       </c>
       <c r="AU298" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV298" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW298" t="n">
         <v>0</v>
       </c>
     </row>
@@ -44554,6 +46334,12 @@
       <c r="AU299" t="n">
         <v>0</v>
       </c>
+      <c r="AV299" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW299" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -44695,6 +46481,12 @@
       <c r="AU300" t="n">
         <v>0</v>
       </c>
+      <c r="AV300" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW300" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -44848,6 +46640,12 @@
       <c r="AU301" t="n">
         <v>0</v>
       </c>
+      <c r="AV301" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW301" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -45011,6 +46809,12 @@
         <v>1</v>
       </c>
       <c r="AU302" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV302" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW302" t="n">
         <v>0</v>
       </c>
     </row>
@@ -45154,6 +46958,12 @@
       <c r="AU303" t="n">
         <v>0</v>
       </c>
+      <c r="AV303" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW303" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -45295,6 +47105,12 @@
       <c r="AU304" t="n">
         <v>0</v>
       </c>
+      <c r="AV304" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW304" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -45446,6 +47262,12 @@
         <v>1</v>
       </c>
       <c r="AU305" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV305" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW305" t="n">
         <v>0</v>
       </c>
     </row>
@@ -45601,6 +47423,12 @@
       <c r="AU306" t="n">
         <v>0</v>
       </c>
+      <c r="AV306" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW306" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -45742,6 +47570,12 @@
       <c r="AU307" t="n">
         <v>0</v>
       </c>
+      <c r="AV307" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW307" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -45895,6 +47729,12 @@
       <c r="AU308" t="n">
         <v>0</v>
       </c>
+      <c r="AV308" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW308" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -46058,6 +47898,12 @@
         <v>1</v>
       </c>
       <c r="AU309" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV309" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW309" t="n">
         <v>0</v>
       </c>
     </row>
@@ -46201,6 +48047,12 @@
       <c r="AU310" t="n">
         <v>0</v>
       </c>
+      <c r="AV310" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW310" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -46354,6 +48206,12 @@
       <c r="AU311" t="n">
         <v>0</v>
       </c>
+      <c r="AV311" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW311" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -46507,6 +48365,12 @@
       <c r="AU312" t="n">
         <v>0</v>
       </c>
+      <c r="AV312" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW312" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -46658,6 +48522,12 @@
         <v>1</v>
       </c>
       <c r="AU313" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV313" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW313" t="n">
         <v>0</v>
       </c>
     </row>
@@ -46793,6 +48663,12 @@
       <c r="AU314" t="n">
         <v>0</v>
       </c>
+      <c r="AV314" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW314" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -46944,6 +48820,12 @@
         <v>1</v>
       </c>
       <c r="AU315" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV315" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW315" t="n">
         <v>0</v>
       </c>
     </row>
@@ -47075,6 +48957,12 @@
       <c r="AU316" t="n">
         <v>0</v>
       </c>
+      <c r="AV316" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW316" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -47208,6 +49096,12 @@
       <c r="AU317" t="n">
         <v>0</v>
       </c>
+      <c r="AV317" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW317" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -47341,6 +49235,12 @@
       <c r="AU318" t="n">
         <v>0</v>
       </c>
+      <c r="AV318" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW318" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -47470,6 +49370,12 @@
       <c r="AU319" t="n">
         <v>0</v>
       </c>
+      <c r="AV319" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW319" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -47599,6 +49505,12 @@
       <c r="AU320" t="n">
         <v>0</v>
       </c>
+      <c r="AV320" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW320" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -47732,6 +49644,12 @@
       <c r="AU321" t="n">
         <v>0</v>
       </c>
+      <c r="AV321" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW321" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -47865,6 +49783,12 @@
       <c r="AU322" t="n">
         <v>0</v>
       </c>
+      <c r="AV322" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW322" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -47998,6 +49922,12 @@
       <c r="AU323" t="n">
         <v>0</v>
       </c>
+      <c r="AV323" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW323" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -48141,6 +50071,12 @@
         <v>0</v>
       </c>
       <c r="AU324" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV324" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW324" t="n">
         <v>1</v>
       </c>
     </row>
@@ -48276,6 +50212,12 @@
       <c r="AU325" t="n">
         <v>0</v>
       </c>
+      <c r="AV325" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW325" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -48427,6 +50369,12 @@
         <v>1</v>
       </c>
       <c r="AU326" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV326" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW326" t="n">
         <v>0</v>
       </c>
     </row>
@@ -48570,6 +50518,12 @@
       <c r="AU327" t="n">
         <v>0</v>
       </c>
+      <c r="AV327" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW327" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -48757,6 +50711,12 @@
         <v>1</v>
       </c>
       <c r="AU328" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV328" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW328" t="n">
         <v>0</v>
       </c>
     </row>
@@ -48900,6 +50860,12 @@
       <c r="AU329" t="n">
         <v>0</v>
       </c>
+      <c r="AV329" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW329" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -49029,6 +50995,12 @@
       <c r="AU330" t="n">
         <v>0</v>
       </c>
+      <c r="AV330" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW330" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -49192,6 +51164,12 @@
         <v>1</v>
       </c>
       <c r="AU331" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV331" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW331" t="n">
         <v>0</v>
       </c>
     </row>
@@ -49335,6 +51313,12 @@
       <c r="AU332" t="n">
         <v>0</v>
       </c>
+      <c r="AV332" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW332" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -49480,6 +51464,12 @@
       <c r="AU333" t="n">
         <v>0</v>
       </c>
+      <c r="AV333" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW333" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -49645,6 +51635,12 @@
       <c r="AU334" t="n">
         <v>0</v>
       </c>
+      <c r="AV334" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW334" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -49798,6 +51794,12 @@
       <c r="AU335" t="n">
         <v>0</v>
       </c>
+      <c r="AV335" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW335" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -49962,6 +51964,12 @@
       </c>
       <c r="AU336" t="n">
         <v>1</v>
+      </c>
+      <c r="AV336" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW336" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="337">
@@ -50104,6 +52112,12 @@
       <c r="AU337" t="n">
         <v>0</v>
       </c>
+      <c r="AV337" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW337" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -50249,6 +52263,12 @@
       <c r="AU338" t="n">
         <v>0</v>
       </c>
+      <c r="AV338" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW338" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -50412,6 +52432,12 @@
         <v>1</v>
       </c>
       <c r="AU339" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV339" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW339" t="n">
         <v>0</v>
       </c>
     </row>
@@ -50543,6 +52569,12 @@
       <c r="AU340" t="n">
         <v>0</v>
       </c>
+      <c r="AV340" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW340" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -50708,6 +52740,12 @@
       <c r="AU341" t="n">
         <v>0</v>
       </c>
+      <c r="AV341" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW341" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -50871,6 +52909,12 @@
         <v>1</v>
       </c>
       <c r="AU342" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV342" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW342" t="n">
         <v>0</v>
       </c>
     </row>
@@ -51018,6 +53062,12 @@
       <c r="AU343" t="n">
         <v>0</v>
       </c>
+      <c r="AV343" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW343" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -51163,6 +53213,12 @@
       <c r="AU344" t="n">
         <v>0</v>
       </c>
+      <c r="AV344" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW344" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -51308,6 +53364,12 @@
       <c r="AU345" t="n">
         <v>1</v>
       </c>
+      <c r="AV345" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW345" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -51461,6 +53523,12 @@
       <c r="AU346" t="n">
         <v>0</v>
       </c>
+      <c r="AV346" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW346" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -51600,6 +53668,12 @@
         <v>0</v>
       </c>
       <c r="AU347" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV347" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW347" t="n">
         <v>0</v>
       </c>
     </row>
@@ -51731,6 +53805,12 @@
       <c r="AU348" t="n">
         <v>0</v>
       </c>
+      <c r="AV348" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW348" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -51872,6 +53952,12 @@
       <c r="AU349" t="n">
         <v>0</v>
       </c>
+      <c r="AV349" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW349" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -52049,6 +54135,12 @@
       <c r="AU350" t="n">
         <v>0</v>
       </c>
+      <c r="AV350" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW350" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -52202,6 +54294,12 @@
       <c r="AU351" t="n">
         <v>0</v>
       </c>
+      <c r="AV351" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW351" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -52365,6 +54463,12 @@
         <v>1</v>
       </c>
       <c r="AU352" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV352" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW352" t="n">
         <v>0</v>
       </c>
     </row>
@@ -52508,6 +54612,12 @@
       <c r="AU353" t="n">
         <v>0</v>
       </c>
+      <c r="AV353" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW353" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -52648,6 +54758,12 @@
       </c>
       <c r="AU354" t="n">
         <v>1</v>
+      </c>
+      <c r="AV354" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW354" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="355">
@@ -52778,6 +54894,12 @@
       <c r="AU355" t="n">
         <v>0</v>
       </c>
+      <c r="AV355" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW355" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -52917,6 +55039,12 @@
         <v>0</v>
       </c>
       <c r="AU356" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV356" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW356" t="n">
         <v>0</v>
       </c>
     </row>
@@ -53048,6 +55176,12 @@
       <c r="AU357" t="n">
         <v>0</v>
       </c>
+      <c r="AV357" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW357" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -53181,6 +55315,12 @@
       <c r="AU358" t="n">
         <v>0</v>
       </c>
+      <c r="AV358" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW358" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -53324,6 +55464,12 @@
         <v>1</v>
       </c>
       <c r="AU359" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV359" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW359" t="n">
         <v>0</v>
       </c>
     </row>
@@ -53459,6 +55605,12 @@
       <c r="AU360" t="n">
         <v>0</v>
       </c>
+      <c r="AV360" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW360" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -53592,6 +55744,12 @@
       <c r="AU361" t="n">
         <v>0</v>
       </c>
+      <c r="AV361" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW361" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -53719,6 +55877,12 @@
         <v>0</v>
       </c>
       <c r="AU362" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV362" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW362" t="n">
         <v>0</v>
       </c>
     </row>
@@ -53862,6 +56026,12 @@
       <c r="AU363" t="n">
         <v>0</v>
       </c>
+      <c r="AV363" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW363" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -54005,6 +56175,12 @@
         <v>1</v>
       </c>
       <c r="AU364" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV364" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW364" t="n">
         <v>0</v>
       </c>
     </row>
@@ -54140,6 +56316,12 @@
       <c r="AU365" t="n">
         <v>0</v>
       </c>
+      <c r="AV365" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW365" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -54283,6 +56465,12 @@
         <v>0</v>
       </c>
       <c r="AU366" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV366" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW366" t="n">
         <v>0</v>
       </c>
     </row>
@@ -54418,6 +56606,12 @@
       <c r="AU367" t="n">
         <v>0</v>
       </c>
+      <c r="AV367" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW367" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -54571,6 +56765,12 @@
       <c r="AU368" t="n">
         <v>0</v>
       </c>
+      <c r="AV368" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW368" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -54724,6 +56924,12 @@
       <c r="AU369" t="n">
         <v>0</v>
       </c>
+      <c r="AV369" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW369" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -54868,6 +57074,12 @@
       </c>
       <c r="AU370" t="n">
         <v>0</v>
+      </c>
+      <c r="AV370" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW370" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="371">
@@ -55002,6 +57214,12 @@
       <c r="AU371" t="n">
         <v>0</v>
       </c>
+      <c r="AV371" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW371" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -55155,6 +57373,12 @@
       <c r="AU372" t="n">
         <v>0</v>
       </c>
+      <c r="AV372" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW372" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -55300,6 +57524,12 @@
       <c r="AU373" t="n">
         <v>0</v>
       </c>
+      <c r="AV373" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW373" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -55439,6 +57669,12 @@
         <v>1</v>
       </c>
       <c r="AU374" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV374" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW374" t="n">
         <v>0</v>
       </c>
     </row>
